--- a/Fixtures/test_data.xlsx
+++ b/Fixtures/test_data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Desktop\Allure_Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Desktop\Selenium_Data_Driven_Login_Automation_Framework\Selenium-Data-Driven-Login-Automation-Framework\Fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9F58C74-1F21-46E4-B0DE-79DD843F2E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0941D0A8-2D12-4F73-A496-E090B66623C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{FD86FCC9-8220-4D4E-BCBD-A0C1574DAAC8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD86FCC9-8220-4D4E-BCBD-A0C1574DAAC8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="17">
   <si>
     <t>username</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>locked_out_user</t>
+  </si>
+  <si>
+    <t>actual</t>
   </si>
 </sst>
 </file>
@@ -140,13 +143,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,13 +465,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B12F31-27BB-4B06-8E60-DDA0507E79D5}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -477,8 +481,11 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -488,8 +495,11 @@
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -499,8 +509,11 @@
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -510,8 +523,11 @@
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -521,8 +537,11 @@
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -532,8 +551,11 @@
       <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -543,8 +565,11 @@
       <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -554,8 +579,11 @@
       <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -565,8 +593,11 @@
       <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -576,8 +607,11 @@
       <c r="C10" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -585,6 +619,9 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>4</v>
       </c>
     </row>
